--- a/4568 JP Daiichi Sankyo.xlsx
+++ b/4568 JP Daiichi Sankyo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF52D65-2336-49D0-8B39-7F486532C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654B44C4-DE32-4C4C-BF81-F06B5602C2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21750" yWindow="825" windowWidth="21105" windowHeight="18525" activeTab="1" xr2:uid="{D043BADF-5FB4-419E-85DA-C93894112E8A}"/>
+    <workbookView xWindow="370" yWindow="3550" windowWidth="19050" windowHeight="16100" xr2:uid="{D043BADF-5FB4-419E-85DA-C93894112E8A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
   <si>
     <t>Price JPY</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Other/Trueup</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -911,16 +914,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D36FBF67-5934-4EC1-85D7-91280292AF8D}">
   <dimension ref="B2:N12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
@@ -943,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+        <v>2887</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>61</v>
       </c>
@@ -959,13 +962,13 @@
         <v>1</v>
       </c>
       <c r="M3" s="1">
-        <v>1914.36284</v>
+        <v>1894.3505290000001</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>52</v>
       </c>
@@ -981,10 +984,10 @@
       </c>
       <c r="M4" s="1">
         <f>+M2*M3/1000</f>
-        <v>11677.613324000002</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+        <v>5468.9899772230001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>53</v>
       </c>
@@ -1001,14 +1004,14 @@
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <f>805.259+204.096+159.374+0.634</f>
-        <v>1169.3630000000001</v>
+        <f>449.807+104.736+4.918+194.435</f>
+        <v>753.89599999999996</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>55</v>
       </c>
@@ -1021,14 +1024,14 @@
         <v>4</v>
       </c>
       <c r="M6" s="1">
-        <f>101.218+0.399+13.8+49.577</f>
-        <v>164.994</v>
+        <f>0.404+13.63+300.077+39.219</f>
+        <v>353.33</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
@@ -1044,10 +1047,10 @@
       </c>
       <c r="M7" s="1">
         <f>+M4-M5+M6</f>
-        <v>10673.244324000003</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+        <v>5068.4239772230003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1057,7 +1060,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1065,7 +1068,7 @@
       <c r="F9" s="7"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1073,7 +1076,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1081,7 +1084,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1098,21 +1101,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8AF968C-0A99-4EB6-8B10-E503E69B2E33}">
   <dimension ref="A1:AI61"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="7" width="9.140625" customWidth="1"/>
-    <col min="8" max="20" width="9.140625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="20" width="9.1796875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="H2" s="11" t="s">
         <v>69</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>18</v>
       </c>
@@ -1262,7 +1265,7 @@
         <v>48304</v>
       </c>
     </row>
-    <row r="4" spans="1:35" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="15" t="s">
         <v>64</v>
       </c>
@@ -1294,7 +1297,7 @@
       <c r="S4" s="19"/>
       <c r="T4" s="19"/>
     </row>
-    <row r="5" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="13" t="s">
         <v>62</v>
       </c>
@@ -1326,7 +1329,7 @@
       <c r="S5" s="18"/>
       <c r="T5" s="18"/>
     </row>
-    <row r="6" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>63</v>
       </c>
@@ -1358,7 +1361,7 @@
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
     </row>
-    <row r="7" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
         <v>65</v>
       </c>
@@ -1390,7 +1393,7 @@
       <c r="S7" s="18"/>
       <c r="T7" s="18"/>
     </row>
-    <row r="8" spans="1:35" s="16" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" s="16" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
         <v>81</v>
       </c>
@@ -1457,7 +1460,7 @@
         <v>287.7</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
       <c r="J9" s="21"/>
@@ -1472,7 +1475,7 @@
       <c r="S9" s="21"/>
       <c r="T9" s="21"/>
     </row>
-    <row r="10" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
@@ -1487,7 +1490,7 @@
       <c r="S10" s="21"/>
       <c r="T10" s="21"/>
     </row>
-    <row r="11" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>42</v>
       </c>
@@ -1528,7 +1531,7 @@
         <v>225.5</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>43</v>
       </c>
@@ -1566,7 +1569,7 @@
         <v>101.9</v>
       </c>
     </row>
-    <row r="13" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>60</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="14" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>66</v>
       </c>
@@ -1652,7 +1655,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="15" spans="1:35" s="16" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" s="16" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
         <v>80</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>425.40000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
@@ -1738,7 +1741,7 @@
       <c r="S16" s="21"/>
       <c r="T16" s="21"/>
     </row>
-    <row r="17" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>86</v>
       </c>
@@ -1780,7 +1783,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="18" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>87</v>
       </c>
@@ -1808,7 +1811,7 @@
       <c r="S18" s="21"/>
       <c r="T18" s="21"/>
     </row>
-    <row r="19" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H19" s="21"/>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
@@ -1823,7 +1826,7 @@
       <c r="S19" s="21"/>
       <c r="T19" s="21"/>
     </row>
-    <row r="20" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>44</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="21" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>79</v>
       </c>
@@ -1910,7 +1913,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="14" t="s">
         <v>45</v>
       </c>
@@ -1955,7 +1958,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="23" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="14" t="s">
         <v>46</v>
       </c>
@@ -2000,7 +2003,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="24" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>47</v>
       </c>
@@ -2039,7 +2042,7 @@
       <c r="S24" s="21"/>
       <c r="T24" s="21"/>
     </row>
-    <row r="25" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>48</v>
       </c>
@@ -2078,7 +2081,7 @@
       <c r="S25" s="21"/>
       <c r="T25" s="21"/>
     </row>
-    <row r="26" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>49</v>
       </c>
@@ -2117,7 +2120,7 @@
       <c r="S26" s="21"/>
       <c r="T26" s="21"/>
     </row>
-    <row r="27" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>50</v>
       </c>
@@ -2167,7 +2170,7 @@
         <v>184.1</v>
       </c>
     </row>
-    <row r="28" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H28" s="21"/>
       <c r="I28" s="21"/>
       <c r="J28" s="21"/>
@@ -2182,7 +2185,7 @@
       <c r="S28" s="21"/>
       <c r="T28" s="21"/>
     </row>
-    <row r="29" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="14" t="s">
         <v>28</v>
       </c>
@@ -2230,7 +2233,7 @@
       <c r="S29" s="21"/>
       <c r="T29" s="21"/>
     </row>
-    <row r="30" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="14" t="s">
         <v>29</v>
       </c>
@@ -2278,7 +2281,7 @@
       <c r="S30" s="21"/>
       <c r="T30" s="21"/>
     </row>
-    <row r="31" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
         <v>30</v>
       </c>
@@ -2326,7 +2329,7 @@
       <c r="S31" s="21"/>
       <c r="T31" s="21"/>
     </row>
-    <row r="32" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
         <v>31</v>
       </c>
@@ -2374,7 +2377,7 @@
       <c r="S32" s="21"/>
       <c r="T32" s="21"/>
     </row>
-    <row r="33" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
         <v>32</v>
       </c>
@@ -2420,7 +2423,7 @@
       <c r="S33" s="21"/>
       <c r="T33" s="21"/>
     </row>
-    <row r="34" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
         <v>33</v>
       </c>
@@ -2468,7 +2471,7 @@
       <c r="S34" s="21"/>
       <c r="T34" s="21"/>
     </row>
-    <row r="35" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
         <v>34</v>
       </c>
@@ -2516,7 +2519,7 @@
       <c r="S35" s="21"/>
       <c r="T35" s="21"/>
     </row>
-    <row r="36" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="14" t="s">
         <v>35</v>
       </c>
@@ -2564,7 +2567,7 @@
       <c r="S36" s="21"/>
       <c r="T36" s="21"/>
     </row>
-    <row r="37" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>36</v>
       </c>
@@ -2612,7 +2615,7 @@
       <c r="S37" s="21"/>
       <c r="T37" s="21"/>
     </row>
-    <row r="38" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="14" t="s">
         <v>37</v>
       </c>
@@ -2660,7 +2663,7 @@
       <c r="S38" s="21"/>
       <c r="T38" s="21"/>
     </row>
-    <row r="39" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14" t="s">
         <v>88</v>
       </c>
@@ -2682,7 +2685,7 @@
       <c r="S39" s="21"/>
       <c r="T39" s="21"/>
     </row>
-    <row r="40" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14" t="s">
         <v>38</v>
       </c>
@@ -2728,7 +2731,7 @@
       <c r="S40" s="21"/>
       <c r="T40" s="21"/>
     </row>
-    <row r="41" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14" t="s">
         <v>39</v>
       </c>
@@ -2760,7 +2763,7 @@
       <c r="S41" s="21"/>
       <c r="T41" s="21"/>
     </row>
-    <row r="42" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
         <v>40</v>
       </c>
@@ -2808,7 +2811,7 @@
       <c r="S42" s="21"/>
       <c r="T42" s="21"/>
     </row>
-    <row r="43" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2870,7 @@
         <v>518.9</v>
       </c>
     </row>
-    <row r="44" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14" t="s">
         <v>41</v>
       </c>
@@ -2921,7 +2924,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="2:26" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="13" t="s">
         <v>89</v>
       </c>
@@ -2951,7 +2954,7 @@
       <c r="S45" s="18"/>
       <c r="T45" s="18"/>
     </row>
-    <row r="46" spans="2:26" s="24" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" s="24" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B46" s="24" t="s">
         <v>15</v>
       </c>
@@ -3015,7 +3018,7 @@
         <v>1278.4780000000001</v>
       </c>
     </row>
-    <row r="47" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="14" t="s">
         <v>17</v>
       </c>
@@ -3060,7 +3063,7 @@
         <v>363.52499999999998</v>
       </c>
     </row>
-    <row r="48" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="14" t="s">
         <v>16</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>914.95300000000009</v>
       </c>
     </row>
-    <row r="49" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>25</v>
       </c>
@@ -3162,7 +3165,7 @@
         <v>471.221</v>
       </c>
     </row>
-    <row r="50" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
         <v>26</v>
       </c>
@@ -3207,7 +3210,7 @@
         <v>341.57</v>
       </c>
     </row>
-    <row r="51" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>24</v>
       </c>
@@ -3261,7 +3264,7 @@
         <v>812.79099999999994</v>
       </c>
     </row>
-    <row r="52" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="14" t="s">
         <v>23</v>
       </c>
@@ -3315,7 +3318,7 @@
         <v>102.16200000000015</v>
       </c>
     </row>
-    <row r="53" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>22</v>
       </c>
@@ -3352,7 +3355,7 @@
         <v>24.721</v>
       </c>
     </row>
-    <row r="54" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="14" t="s">
         <v>21</v>
       </c>
@@ -3403,7 +3406,7 @@
         <v>126.88300000000015</v>
       </c>
     </row>
-    <row r="55" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>20</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="56" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:26" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="14" t="s">
         <v>19</v>
       </c>
@@ -3487,11 +3490,11 @@
         <v>109.18300000000015</v>
       </c>
     </row>
-    <row r="57" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
       <c r="Y57" s="15"/>
       <c r="Z57" s="15"/>
     </row>
-    <row r="58" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:26" x14ac:dyDescent="0.25">
       <c r="I58" s="22"/>
       <c r="J58" s="22"/>
       <c r="K58" s="22"/>
@@ -3507,7 +3510,7 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="14"/>
     </row>
-    <row r="60" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B60" s="14" t="s">
         <v>67</v>
       </c>
@@ -3532,7 +3535,7 @@
         <v>0.73316637949178964</v>
       </c>
     </row>
-    <row r="61" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B61" s="14" t="s">
         <v>51</v>
       </c>
